--- a/H5509_V2/H5509_alarm.xlsx
+++ b/H5509_V2/H5509_alarm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\H5509_V3\bin\Debug\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\H5509_V2\H5509_V2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049B560B-79D7-4D9C-BC85-A2A82FB2ADA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924A3255-4009-48F1-B743-2C7201C7E273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16140" yWindow="3450" windowWidth="20970" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1035" windowWidth="29580" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7826,9 +7826,6 @@
     <t>ALL Home Exception</t>
   </si>
   <si>
-    <t>全部回零异常!详细信息:Msg</t>
-  </si>
-  <si>
     <t>Com Not Open</t>
   </si>
   <si>
@@ -7990,6 +7987,10 @@
   </si>
   <si>
     <t>测试手臂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回零异常!详细信息:Msg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8041,7 +8042,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8054,6 +8055,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -31284,8 +31286,8 @@
       <c r="C1350" s="2" t="s">
         <v>2594</v>
       </c>
-      <c r="D1350" s="2" t="s">
-        <v>2595</v>
+      <c r="D1350" s="6" t="s">
+        <v>2649</v>
       </c>
       <c r="E1350" s="1" t="s">
         <v>2493</v>
@@ -31299,10 +31301,10 @@
         <v>1400430</v>
       </c>
       <c r="C1351" s="2" t="s">
+        <v>2595</v>
+      </c>
+      <c r="D1351" s="2" t="s">
         <v>2596</v>
-      </c>
-      <c r="D1351" s="2" t="s">
-        <v>2597</v>
       </c>
       <c r="E1351" s="1" t="s">
         <v>2323</v>
@@ -31316,10 +31318,10 @@
         <v>1400440</v>
       </c>
       <c r="C1352" s="2" t="s">
+        <v>2597</v>
+      </c>
+      <c r="D1352" s="2" t="s">
         <v>2598</v>
-      </c>
-      <c r="D1352" s="2" t="s">
-        <v>2599</v>
       </c>
       <c r="E1352" s="1" t="s">
         <v>2323</v>
@@ -31333,10 +31335,10 @@
         <v>1400441</v>
       </c>
       <c r="C1353" s="2" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="D1353" s="2" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="E1353" s="1" t="s">
         <v>2493</v>
@@ -31350,10 +31352,10 @@
         <v>1400442</v>
       </c>
       <c r="C1354" s="3" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="D1354" s="3" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="E1354" s="1" t="s">
         <v>2493</v>
@@ -31367,10 +31369,10 @@
         <v>1400500</v>
       </c>
       <c r="C1355" s="3" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="D1355" s="3" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="E1355" s="4" t="s">
         <v>2493</v>
@@ -31384,10 +31386,10 @@
         <v>1400600</v>
       </c>
       <c r="C1356" s="3" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="D1356" s="3" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="E1356" s="4" t="s">
         <v>2493</v>
@@ -31401,10 +31403,10 @@
         <v>1400443</v>
       </c>
       <c r="C1357" s="2" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="D1357" s="2" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="E1357" s="4" t="s">
         <v>2493</v>
@@ -31418,10 +31420,10 @@
         <v>1400444</v>
       </c>
       <c r="C1358" s="2" t="s">
+        <v>2604</v>
+      </c>
+      <c r="D1358" s="2" t="s">
         <v>2605</v>
-      </c>
-      <c r="D1358" s="2" t="s">
-        <v>2606</v>
       </c>
       <c r="E1358" s="1" t="s">
         <v>2493</v>
@@ -31435,10 +31437,10 @@
         <v>1400445</v>
       </c>
       <c r="C1359" s="2" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="D1359" s="2" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="E1359" s="1" t="s">
         <v>1093</v>
@@ -31452,10 +31454,10 @@
         <v>1400446</v>
       </c>
       <c r="C1360" s="2" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="D1360" s="2" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="E1360" s="1" t="s">
         <v>2428</v>
@@ -31469,10 +31471,10 @@
         <v>1400447</v>
       </c>
       <c r="C1361" s="2" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="D1361" s="2" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="E1361" s="1" t="s">
         <v>2428</v>
@@ -31486,10 +31488,10 @@
         <v>1400448</v>
       </c>
       <c r="C1362" s="2" t="s">
+        <v>2609</v>
+      </c>
+      <c r="D1362" s="2" t="s">
         <v>2610</v>
-      </c>
-      <c r="D1362" s="2" t="s">
-        <v>2611</v>
       </c>
       <c r="E1362" s="1" t="s">
         <v>2428</v>
@@ -31503,10 +31505,10 @@
         <v>1400449</v>
       </c>
       <c r="C1363" s="2" t="s">
+        <v>2611</v>
+      </c>
+      <c r="D1363" s="2" t="s">
         <v>2612</v>
-      </c>
-      <c r="D1363" s="2" t="s">
-        <v>2613</v>
       </c>
       <c r="E1363" s="1" t="s">
         <v>2428</v>
@@ -31520,10 +31522,10 @@
         <v>1400450</v>
       </c>
       <c r="C1364" s="2" t="s">
+        <v>2613</v>
+      </c>
+      <c r="D1364" s="2" t="s">
         <v>2614</v>
-      </c>
-      <c r="D1364" s="2" t="s">
-        <v>2615</v>
       </c>
       <c r="E1364" s="1" t="s">
         <v>2428</v>
@@ -31537,10 +31539,10 @@
         <v>1400451</v>
       </c>
       <c r="C1365" s="2" t="s">
+        <v>2615</v>
+      </c>
+      <c r="D1365" s="2" t="s">
         <v>2616</v>
-      </c>
-      <c r="D1365" s="2" t="s">
-        <v>2617</v>
       </c>
       <c r="E1365" s="1" t="s">
         <v>2428</v>
@@ -31554,10 +31556,10 @@
         <v>1400452</v>
       </c>
       <c r="C1366" s="2" t="s">
+        <v>2617</v>
+      </c>
+      <c r="D1366" s="2" t="s">
         <v>2618</v>
-      </c>
-      <c r="D1366" s="2" t="s">
-        <v>2619</v>
       </c>
       <c r="E1366" s="1" t="s">
         <v>2428</v>
@@ -31571,10 +31573,10 @@
         <v>1400453</v>
       </c>
       <c r="C1367" s="2" t="s">
+        <v>2619</v>
+      </c>
+      <c r="D1367" s="2" t="s">
         <v>2620</v>
-      </c>
-      <c r="D1367" s="2" t="s">
-        <v>2621</v>
       </c>
       <c r="E1367" s="1" t="s">
         <v>2428</v>
@@ -31588,10 +31590,10 @@
         <v>1400454</v>
       </c>
       <c r="C1368" s="2" t="s">
+        <v>2621</v>
+      </c>
+      <c r="D1368" s="2" t="s">
         <v>2622</v>
-      </c>
-      <c r="D1368" s="2" t="s">
-        <v>2623</v>
       </c>
       <c r="E1368" s="1" t="s">
         <v>2428</v>
@@ -31605,10 +31607,10 @@
         <v>1400455</v>
       </c>
       <c r="C1369" s="2" t="s">
+        <v>2623</v>
+      </c>
+      <c r="D1369" s="2" t="s">
         <v>2624</v>
-      </c>
-      <c r="D1369" s="2" t="s">
-        <v>2625</v>
       </c>
       <c r="E1369" s="1" t="s">
         <v>2428</v>
@@ -31622,10 +31624,10 @@
         <v>1400456</v>
       </c>
       <c r="C1370" s="2" t="s">
+        <v>2625</v>
+      </c>
+      <c r="D1370" s="2" t="s">
         <v>2626</v>
-      </c>
-      <c r="D1370" s="2" t="s">
-        <v>2627</v>
       </c>
       <c r="E1370" s="1" t="s">
         <v>2428</v>
@@ -31639,10 +31641,10 @@
         <v>1400457</v>
       </c>
       <c r="C1371" s="2" t="s">
+        <v>2627</v>
+      </c>
+      <c r="D1371" s="2" t="s">
         <v>2628</v>
-      </c>
-      <c r="D1371" s="2" t="s">
-        <v>2629</v>
       </c>
       <c r="E1371" s="1" t="s">
         <v>2428</v>
@@ -31656,13 +31658,13 @@
         <v>1400460</v>
       </c>
       <c r="C1372" s="2" t="s">
+        <v>2629</v>
+      </c>
+      <c r="D1372" s="2" t="s">
         <v>2630</v>
       </c>
-      <c r="D1372" s="2" t="s">
-        <v>2631</v>
-      </c>
       <c r="E1372" s="5" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="1373" spans="1:5" x14ac:dyDescent="0.2">
@@ -31673,10 +31675,10 @@
         <v>1400461</v>
       </c>
       <c r="C1373" s="2" t="s">
+        <v>2631</v>
+      </c>
+      <c r="D1373" s="2" t="s">
         <v>2632</v>
-      </c>
-      <c r="D1373" s="2" t="s">
-        <v>2633</v>
       </c>
       <c r="E1373" s="1" t="s">
         <v>564</v>
@@ -31690,10 +31692,10 @@
         <v>1400462</v>
       </c>
       <c r="C1374" s="2" t="s">
+        <v>2633</v>
+      </c>
+      <c r="D1374" s="2" t="s">
         <v>2634</v>
-      </c>
-      <c r="D1374" s="2" t="s">
-        <v>2635</v>
       </c>
       <c r="E1374" s="1" t="s">
         <v>571</v>
@@ -31707,10 +31709,10 @@
         <v>1400463</v>
       </c>
       <c r="C1375" s="2" t="s">
+        <v>2635</v>
+      </c>
+      <c r="D1375" s="2" t="s">
         <v>2636</v>
-      </c>
-      <c r="D1375" s="2" t="s">
-        <v>2637</v>
       </c>
       <c r="E1375" s="1" t="s">
         <v>578</v>
@@ -31724,10 +31726,10 @@
         <v>1400464</v>
       </c>
       <c r="C1376" s="2" t="s">
+        <v>2637</v>
+      </c>
+      <c r="D1376" s="2" t="s">
         <v>2638</v>
-      </c>
-      <c r="D1376" s="2" t="s">
-        <v>2639</v>
       </c>
       <c r="E1376" s="1" t="s">
         <v>585</v>
@@ -31741,10 +31743,10 @@
         <v>1400465</v>
       </c>
       <c r="C1377" s="2" t="s">
+        <v>2639</v>
+      </c>
+      <c r="D1377" s="2" t="s">
         <v>2640</v>
-      </c>
-      <c r="D1377" s="2" t="s">
-        <v>2641</v>
       </c>
       <c r="E1377" s="1" t="s">
         <v>592</v>
@@ -31758,10 +31760,10 @@
         <v>1400466</v>
       </c>
       <c r="C1378" s="2" t="s">
+        <v>2641</v>
+      </c>
+      <c r="D1378" s="2" t="s">
         <v>2642</v>
-      </c>
-      <c r="D1378" s="2" t="s">
-        <v>2643</v>
       </c>
       <c r="E1378" s="1" t="s">
         <v>599</v>
@@ -31775,10 +31777,10 @@
         <v>1400467</v>
       </c>
       <c r="C1379" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="D1379" s="2" t="s">
         <v>2644</v>
-      </c>
-      <c r="D1379" s="2" t="s">
-        <v>2645</v>
       </c>
       <c r="E1379" s="1" t="s">
         <v>606</v>
@@ -31792,13 +31794,13 @@
         <v>1400468</v>
       </c>
       <c r="C1380" s="2" t="s">
+        <v>2645</v>
+      </c>
+      <c r="D1380" s="2" t="s">
         <v>2646</v>
       </c>
-      <c r="D1380" s="2" t="s">
-        <v>2647</v>
-      </c>
       <c r="E1380" s="5" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
     </row>
   </sheetData>
